--- a/data/trans_dic/IP7_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP7_R-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con salud general regular o mala</t>
+          <t>Menores con salud general regular o mala (tasa de respuesta: 99,72%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,63</t>
+          <t>0,0; 2,62</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,66</t>
+          <t>0,0; 4,51</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 6,6</t>
+          <t>0,77; 6,79</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 6,9</t>
+          <t>0,7; 6,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,48</t>
+          <t>0,0; 4,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,29</t>
+          <t>0,0; 5,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,7</t>
+          <t>0,56; 3,6</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,19</t>
+          <t>0,0; 2,24</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,49</t>
+          <t>0,0; 2,54</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,65; 4,45</t>
+          <t>0,68; 4,75</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,83</t>
+          <t>0,72; 6,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,75</t>
+          <t>0,0; 3,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,24</t>
+          <t>0,0; 3,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 8,22</t>
+          <t>1,15; 8,67</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,68</t>
+          <t>0,72; 7,12</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,15</t>
+          <t>0,0; 4,06</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,5; 5,6</t>
+          <t>0,5; 5,32</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 7,76</t>
+          <t>0,89; 8,15</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,14; 5,45</t>
+          <t>0,9; 5,11</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,05</t>
+          <t>0,34; 2,89</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,31; 3,08</t>
+          <t>0,31; 3,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>1,37; 6,38</t>
+          <t>1,22; 6,1</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,27</t>
+          <t>0,0; 4,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,36</t>
+          <t>0,0; 5,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,99; 9,58</t>
+          <t>1,0; 9,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 2,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 7,84</t>
+          <t>0,71; 7,09</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,52</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,94</t>
+          <t>0,0; 5,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,51</t>
+          <t>0,0; 8,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,79</t>
+          <t>0,82; 4,79</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,4</t>
+          <t>0,0; 2,26</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,83</t>
+          <t>0,91; 5,68</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,56</t>
+          <t>0,0; 5,58</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,93</t>
+          <t>0,64; 3,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 5,73</t>
+          <t>1,58; 5,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 3,91</t>
+          <t>0,79; 4,0</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,11; 15,67</t>
+          <t>1,14; 16,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 4,69</t>
+          <t>1,0; 4,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,31; 6,78</t>
+          <t>2,58; 7,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 5,78</t>
+          <t>1,35; 5,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,25; 4,94</t>
+          <t>1,28; 4,86</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,46</t>
+          <t>1,03; 3,43</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,19; 5,36</t>
+          <t>2,34; 5,36</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,38; 4,03</t>
+          <t>1,39; 4,11</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,73; 8,88</t>
+          <t>1,66; 8,37</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,66</t>
+          <t>0,6; 5,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,08; 6,16</t>
+          <t>0,96; 5,64</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,95; 7,29</t>
+          <t>1,88; 7,36</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,79</t>
+          <t>0,93; 6,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 8,26</t>
+          <t>2,19; 8,42</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,83</t>
+          <t>0,77; 4,92</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,98</t>
+          <t>0,89; 5,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 5,88</t>
+          <t>0,77; 5,29</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,0; 6,06</t>
+          <t>1,98; 6,04</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,43</t>
+          <t>1,21; 4,29</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,23</t>
+          <t>1,84; 5,06</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,79</t>
+          <t>1,32; 4,86</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,91</t>
+          <t>0,0; 4,45</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,49; 13,08</t>
+          <t>1,55; 13,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,05</t>
+          <t>0,0; 6,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,16; 10,07</t>
+          <t>1,15; 9,94</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,76; 10,71</t>
+          <t>1,8; 10,65</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,82; 7,12</t>
+          <t>0,81; 6,28</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,98</t>
+          <t>0,0; 5,9</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,81; 8,23</t>
+          <t>0,82; 8,29</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,27; 6,05</t>
+          <t>1,27; 5,8</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,68; 7,82</t>
+          <t>1,65; 7,6</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,98</t>
+          <t>0,46; 3,99</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1,5; 6,91</t>
+          <t>1,46; 7,63</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,49</t>
+          <t>0,81; 2,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,71</t>
+          <t>1,57; 3,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,29; 3,12</t>
+          <t>1,24; 2,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1,89; 6,87</t>
+          <t>1,92; 6,26</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,57</t>
+          <t>2,34; 4,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,33</t>
+          <t>1,46; 3,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,15</t>
+          <t>1,32; 3,09</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,58; 3,72</t>
+          <t>1,6; 3,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,82; 3,17</t>
+          <t>1,81; 3,23</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,75; 3,07</t>
+          <t>1,75; 3,08</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,84</t>
+          <t>1,51; 2,8</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,0; 4,3</t>
+          <t>2,0; 4,38</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores con salud general regular o mala (tasa de respuesta: 99,72%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2560</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2682</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2280</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>3130</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>790</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>1285</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>4840</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2729</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4019</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>800; 7096</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>686; 6676</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4563</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 7690</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>1136; 7271</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4005</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4594</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>1642; 11463</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>2069</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1067</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3114</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2143</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>1286</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>2817</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>4211</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2354</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2704</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5931</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>629; 6010</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3465</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3378</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1090; 8206</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>612; 6077</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3901</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>556; 5960</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>855; 7792</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1552; 8824</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>645; 5476</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>670; 6541</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>2330; 11610</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>622</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1276</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2116</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>3340</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1258</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1525</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>3962</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1276</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>3374</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1525</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3146</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4805</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>619; 5904</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>703; 7046</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4403</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5268</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>1365; 7989</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3904</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>1243; 7790</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 6454</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>3388</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6311</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4245</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>9347</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4730</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>9620</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>6159</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>5943</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>8118</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>15932</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>10404</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>15290</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>1291; 7003</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>3242; 11402</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>1764; 8909</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2502; 36285</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2003; 9527</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>5857; 16283</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>2850; 12453</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>2789; 10605</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>4124; 13765</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>10139; 23194</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>6022; 17816</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>7262; 36579</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2551</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>4174</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>5156</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>3370</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>5986</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>3075</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3415</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>3881</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>8537</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>7249</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>8571</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>7251</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>624; 5785</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1427; 8409</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2555; 10022</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>1109; 7840</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2776; 10661</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1076; 6869</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>1273; 7686</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>1258; 8606</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>4565; 13938</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>3492; 12395</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5128; 14135</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>3722; 13695</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>587</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>3000</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>1206</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2753</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3901</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1908</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>2223</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>4489</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>4908</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>1859</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>4976</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3335</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>834; 7533</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3746</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>793; 6847</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>1306; 7713</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>593; 4606</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3956</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>593; 5969</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>1870; 8540</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>2099; 9675</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>587; 5054</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>2057; 10746</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>9665</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>16619</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>13398</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>21144</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>22783</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>15890</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>14799</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>18669</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>32447</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>32509</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>28197</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>39813</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>5202; 14885</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>10650; 23704</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>8257; 19525</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>12644; 41213</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>15963; 31542</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>10400; 23015</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>9350; 21835</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>12019; 28055</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>23885; 42684</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>24319; 42753</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>20693; 38497</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>28088; 61587</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>